--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T18:36:39.349693+00:00</t>
+          <t>2026-09-10T09:17:22.826745+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T09:17:22.826745+00:00</t>
+          <t>2026-09-10T23:26:02.967644+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T23:26:02.967644+00:00</t>
+          <t>2026-09-16T17:04:54.396779+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T17:04:54.396779+00:00</t>
+          <t>2026-09-16T17:30:51.436995+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T17:30:51.436995+00:00</t>
+          <t>2026-09-17T10:52:00.376667+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:52:00.376667+00:00</t>
+          <t>2026-09-18T10:27:17.445299+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:27:17.445299+00:00</t>
+          <t>2026-09-19T10:12:16.847588+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T10:12:16.847588+00:00</t>
+          <t>2026-09-20T10:31:17.131883+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T10:31:17.131883+00:00</t>
+          <t>2026-09-21T11:49:15.712254+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T11:49:15.712254+00:00</t>
+          <t>2026-09-22T10:51:02.704807+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T10:51:02.704807+00:00</t>
+          <t>2026-09-23T10:40:33.287048+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T10:40:33.287048+00:00</t>
+          <t>2026-09-24T11:00:10.212695+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T11:00:10.212695+00:00</t>
+          <t>2026-09-25T11:00:29.324068+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:00:29.324068+00:00</t>
+          <t>2026-09-26T10:42:48.709121+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T10:42:48.709121+00:00</t>
+          <t>2026-09-27T11:16:19.415240+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T11:16:19.415240+00:00</t>
+          <t>2026-09-28T12:44:25.923635+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T12:44:25.923635+00:00</t>
+          <t>2026-09-29T12:00:37.125060+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T12:00:37.125060+00:00</t>
+          <t>2026-09-30T11:49:19.589223+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:49:19.589223+00:00</t>
+          <t>2026-10-01T12:18:40.123207+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T12:18:40.123207+00:00</t>
+          <t>2026-10-02T11:46:53.281092+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T11:46:53.281092+00:00</t>
+          <t>2026-10-03T11:00:32.054338+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03T11:00:32.054338+00:00</t>
+          <t>2026-10-04T11:42:10.348437+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T11:42:10.348437+00:00</t>
+          <t>2026-10-05T13:25:26.903642+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T13:25:26.903642+00:00</t>
+          <t>2026-10-06T12:39:04.331245+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T12:39:04.331245+00:00</t>
+          <t>2026-10-07T12:32:18.501461+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T12:32:18.501461+00:00</t>
+          <t>2026-10-08T12:42:02.108893+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">

--- a/data/processed/kpi_results.xlsx
+++ b/data/processed/kpi_results.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T12:42:02.108893+00:00</t>
+          <t>2026-10-09T12:28:56.488688+00:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
